--- a/Textuais/analise/tabela_sintese.xlsx
+++ b/Textuais/analise/tabela_sintese.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,63 +413,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>DV</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Espectro político (β)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Espectro político (p)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Econ (β)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Econ (p)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Controles (p&lt;0,10; sinal)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Média (econ=0)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Média (econ=1)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Média contraf.</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Econ (p_BH)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Espectro (p_BH)</t>
         </is>
       </c>
     </row>
@@ -496,15 +494,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Logit ord.</t>
+          <t>Logit ord. ⚠ Hessiana singular</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6861940483696216</v>
+        <v>0.6861339207178659</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-1.008171910507487</v>
+        <v>-1.008534342628402</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -521,6 +519,8 @@
       <c r="K2" t="n">
         <v>1.488</v>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -537,16 +537,20 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7083454438668564</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>0.7083219041664739</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.540362565647115e-07</v>
+      </c>
       <c r="F3" t="n">
-        <v>-1.461322721082632</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>-1.46129518941398</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.02312185801147922</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(nenhum)</t>
+          <t>Você se considera uma pessoa politicamente engajada? _Sim: −</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -558,6 +562,12 @@
       <c r="K3" t="n">
         <v>1.503</v>
       </c>
+      <c r="L3" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -574,16 +584,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2460931279543571</v>
+        <v>0.2461162261164281</v>
       </c>
       <c r="E4" t="n">
-        <v>0.033602767675503</v>
+        <v>0.03358295322329783</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.442755554078297</v>
+        <v>-1.441562012449127</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01840607756219748</v>
+        <v>0.01848753457000955</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -599,6 +609,12 @@
       <c r="K4" t="n">
         <v>0.901</v>
       </c>
+      <c r="L4" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0488</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -615,16 +631,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.04728887021408018</v>
+        <v>0.04727036190450066</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7622148479560011</v>
+        <v>0.7623011189280646</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5152051173207841</v>
+        <v>-0.5150991073491263</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4729047430015033</v>
+        <v>0.4729911863547429</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -640,6 +656,12 @@
       <c r="K5" t="n">
         <v>0.363</v>
       </c>
+      <c r="L5" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7785</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -656,16 +678,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2835270260531337</v>
+        <v>0.2835059330478741</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01508071271122066</v>
+        <v>0.01508890800918349</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6422762889115384</v>
+        <v>0.6426959467573305</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2466883465039889</v>
+        <v>0.2463934505134354</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -681,6 +703,12 @@
       <c r="K6" t="n">
         <v>1.038</v>
       </c>
+      <c r="L6" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0259</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -697,16 +725,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09632425203403804</v>
+        <v>0.09638077606237198</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4305323944020295</v>
+        <v>0.4302636563166827</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7297799076232409</v>
+        <v>0.7294645988758237</v>
       </c>
       <c r="G7" t="n">
-        <v>0.248293410981379</v>
+        <v>0.24848716418118</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -720,7 +748,13 @@
         <v>1.706</v>
       </c>
       <c r="K7" t="n">
-        <v>1.487</v>
+        <v>1.488</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4589</v>
       </c>
     </row>
     <row r="8">
@@ -738,16 +772,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5230030682308782</v>
+        <v>0.5231247625204785</v>
       </c>
       <c r="E8" t="n">
-        <v>2.754120920357195e-05</v>
+        <v>2.746537407478143e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.023634031317514</v>
+        <v>-1.023885463841278</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08645754054196722</v>
+        <v>0.0864001582330568</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -761,7 +795,13 @@
         <v>0.647</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001</v>
       </c>
     </row>
     <row r="9">
@@ -779,16 +819,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4644296600744926</v>
+        <v>0.4644943375022704</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002059637428354426</v>
+        <v>0.002056577085174266</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4459042273892518</v>
+        <v>-0.4469447031230367</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5670077725728775</v>
+        <v>0.5661271248498143</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -802,7 +842,13 @@
         <v>0.176</v>
       </c>
       <c r="K9" t="n">
-        <v>0.271</v>
+        <v>0.272</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7548</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0043</v>
       </c>
     </row>
     <row r="10">
@@ -820,16 +866,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2882837383514863</v>
+        <v>0.288153955279164</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01767256188349482</v>
+        <v>0.01772433855995197</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2773768417251639</v>
+        <v>-0.2764800537376533</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6377011039032311</v>
+        <v>0.6387715944959587</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -843,7 +889,13 @@
         <v>0.588</v>
       </c>
       <c r="K10" t="n">
-        <v>0.715</v>
+        <v>0.714</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8211000000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0293</v>
       </c>
     </row>
     <row r="11">
@@ -861,16 +913,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9936296312973112</v>
+        <v>0.9936564449329625</v>
       </c>
       <c r="E11" t="n">
-        <v>1.525981042040814e-11</v>
+        <v>1.525312999563423e-11</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.066588394161464</v>
+        <v>-1.066474338003889</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08654526373370235</v>
+        <v>0.08658253148667906</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -886,6 +938,12 @@
       <c r="K11" t="n">
         <v>1.213</v>
       </c>
+      <c r="L11" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -902,16 +960,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2139073402206408</v>
+        <v>0.2139236570420907</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06496417567544929</v>
+        <v>0.06494494127448769</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5063616343897716</v>
+        <v>-0.5062733596518636</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3779699449703443</v>
+        <v>0.378058098043688</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -927,6 +985,12 @@
       <c r="K12" t="n">
         <v>1.101</v>
       </c>
+      <c r="L12" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0891</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -943,16 +1007,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.7880021566927609</v>
+        <v>-0.7880422272945444</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3891015767994e-06</v>
+        <v>1.388452106838932e-06</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4223214093694668</v>
+        <v>-0.422266717428792</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5170574564411468</v>
+        <v>0.5171169551371471</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -968,6 +1032,12 @@
       <c r="K13" t="n">
         <v>0.884</v>
       </c>
+      <c r="L13" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -984,16 +1054,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.6340600423567123</v>
+        <v>-0.6340041761479539</v>
       </c>
       <c r="E14" t="n">
-        <v>3.523615532210419e-06</v>
+        <v>3.529066834518616e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6232641775092231</v>
+        <v>-0.6228461561390669</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2825208926971312</v>
+        <v>0.2828356055069706</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1009,6 +1079,12 @@
       <c r="K14" t="n">
         <v>0.992</v>
       </c>
+      <c r="L14" t="n">
+        <v>0.6788</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1025,16 +1101,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.009241822791398947</v>
+        <v>0.00925094368818391</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9374707032663521</v>
+        <v>0.9374090221678536</v>
       </c>
       <c r="F15" t="n">
-        <v>1.72202208326251</v>
+        <v>1.722172979151746</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01009199463435156</v>
+        <v>0.01008476979032947</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1048,7 +1124,13 @@
         <v>1.765</v>
       </c>
       <c r="K15" t="n">
-        <v>1.239</v>
+        <v>1.238</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.9374</v>
       </c>
     </row>
     <row r="16">
@@ -1066,16 +1148,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1483047487554</v>
+        <v>-0.1483254769968033</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2605043511370132</v>
+        <v>0.2604389439525243</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2308088228666189</v>
+        <v>-0.2305434923061137</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6969173931564701</v>
+        <v>0.6972402420430831</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1091,6 +1173,12 @@
       <c r="K16" t="n">
         <v>0.68</v>
       </c>
+      <c r="L16" t="n">
+        <v>0.8552</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3205</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1107,16 +1195,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1514377983600889</v>
+        <v>-0.1514768919151942</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2934235802090568</v>
+        <v>0.293312311006934</v>
       </c>
       <c r="F17" t="n">
-        <v>1.166498889598845</v>
+        <v>1.16725895766872</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0806137863310573</v>
+        <v>0.08041028327255001</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1132,6 +1220,12 @@
       <c r="K17" t="n">
         <v>0.188</v>
       </c>
+      <c r="L17" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.3492</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1148,16 +1242,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.2631154733872994</v>
+        <v>-0.2630836117865611</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02769960653283825</v>
+        <v>0.02771897536940258</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1277877133973735</v>
+        <v>0.127684165533489</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8212288685400834</v>
+        <v>0.8213734595621498</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1171,7 +1265,13 @@
         <v>0.9409999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.903</v>
+        <v>0.904</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.9368</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.0416</v>
       </c>
     </row>
     <row r="19">
@@ -1189,16 +1289,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.3983062488892564</v>
+        <v>-0.3982292321456789</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0006606387210300633</v>
+        <v>0.0006621536970266153</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.01574659459461467</v>
+        <v>-0.01571595824535064</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9776173662191169</v>
+        <v>0.9776609209925777</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1214,6 +1314,12 @@
       <c r="K19" t="n">
         <v>1.287</v>
       </c>
+      <c r="L19" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.0017</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1226,15 +1332,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Logit ord.</t>
+          <t>Logit ord. ⚠ Hessiana singular</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9383612582394699</v>
+        <v>0.9383305657684475</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>-0.3480750594465538</v>
+        <v>-0.3473648961753649</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
@@ -1251,6 +1357,8 @@
       <c r="K20" t="n">
         <v>1.496</v>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1267,16 +1375,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.7101534444192357</v>
+        <v>-0.7099839214426175</v>
       </c>
       <c r="E21" t="n">
-        <v>4.884986761718992e-06</v>
+        <v>4.905302259067096e-06</v>
       </c>
       <c r="F21" t="n">
-        <v>0.510790920910505</v>
+        <v>0.5097464658635793</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5099413821295086</v>
+        <v>0.5107921827403987</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1292,6 +1400,12 @@
       <c r="K21" t="n">
         <v>1.681</v>
       </c>
+      <c r="L21" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1304,15 +1418,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Logit ord.</t>
+          <t>Logit ord. ⚠ Hessiana singular</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.296034448617642</v>
+        <v>1.297771503956332</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>57.81570403671597</v>
+        <v>61.75026702535329</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
@@ -1329,6 +1443,8 @@
       <c r="K22" t="n">
         <v>1.89</v>
       </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1341,15 +1457,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Logit ord.</t>
+          <t>Logit ord. ⚠ Hessiana singular</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.05856946672666039</v>
+        <v>-0.05858709382901615</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>-0.6789065521093478</v>
+        <v>-0.6800255726444329</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
@@ -1366,6 +1482,8 @@
       <c r="K23" t="n">
         <v>1.963</v>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1382,16 +1500,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.4579284194720355</v>
+        <v>0.4579776447243931</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0003481391511553751</v>
+        <v>0.0003477291297885693</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9321429412822579</v>
+        <v>-0.9320646051092429</v>
       </c>
       <c r="G24" t="n">
-        <v>0.169834444190587</v>
+        <v>0.1698750632977669</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1407,6 +1525,12 @@
       <c r="K24" t="n">
         <v>0.454</v>
       </c>
+      <c r="L24" t="n">
+        <v>0.5436</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.0009</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1415,7 +1539,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1423,16 +1547,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.3237530832134355</v>
+        <v>0.323319314647517</v>
       </c>
       <c r="E25" t="n">
-        <v>0.007377498521883152</v>
+        <v>0.007316479810163928</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1459217531348083</v>
+        <v>0.1410369104645043</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7893923887008276</v>
+        <v>0.7962082039888559</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1440,13 +1564,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.289</v>
+        <v>1.287</v>
       </c>
       <c r="J25" t="n">
         <v>1.176</v>
       </c>
       <c r="K25" t="n">
-        <v>1.099</v>
+        <v>1.102</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.9321</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="26">
@@ -1464,16 +1594,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.09626214455971359</v>
+        <v>-0.096283283529839</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5383243404111357</v>
+        <v>0.5382238156326939</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1883234205001087</v>
+        <v>0.1878783638221876</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8388748444288388</v>
+        <v>0.8392427439252115</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1489,6 +1619,12 @@
       <c r="K26" t="n">
         <v>1.783</v>
       </c>
+      <c r="L26" t="n">
+        <v>0.9368</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5616</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1505,16 +1641,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.3193471069243226</v>
+        <v>-0.3194751800053833</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00516157853227601</v>
+        <v>0.005144636819895877</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3276128668462079</v>
+        <v>0.3275393552002586</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5577580323960153</v>
+        <v>0.557849371636796</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1530,6 +1666,12 @@
       <c r="K27" t="n">
         <v>0.961</v>
       </c>
+      <c r="L27" t="n">
+        <v>0.7548</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.009900000000000001</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1542,15 +1684,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Logit ord.</t>
+          <t>Logit ord. ⚠ Hessiana singular</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.3281276195042765</v>
+        <v>0.3282417725185383</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>-0.555456844251257</v>
+        <v>-0.5549730084888</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
@@ -1567,6 +1709,8 @@
       <c r="K28" t="n">
         <v>1.852</v>
       </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1583,13 +1727,17 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.2478123741964953</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>0.2477752143275182</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0448915285285271</v>
+      </c>
       <c r="F29" t="n">
-        <v>0.06376950320332678</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+        <v>0.06283897301833682</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9173098225490607</v>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>(nenhum)</t>
@@ -1604,6 +1752,12 @@
       <c r="K29" t="n">
         <v>1.52</v>
       </c>
+      <c r="L29" t="n">
+        <v>0.9785</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.0634</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1620,16 +1774,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.6947013824697169</v>
+        <v>0.6948405646912257</v>
       </c>
       <c r="E30" t="n">
-        <v>2.586569669652654e-06</v>
+        <v>2.580016838119011e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.03402176894113666</v>
+        <v>-0.03428177886961069</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9578023251858969</v>
+        <v>0.9574832811835554</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1645,6 +1799,12 @@
       <c r="K30" t="n">
         <v>0.481</v>
       </c>
+      <c r="L30" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1661,16 +1821,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.2656625505559411</v>
+        <v>-0.2657171340850477</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02724925525193195</v>
+        <v>0.02721785186154665</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3763489789721829</v>
+        <v>-0.3761875516787433</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5136249872429773</v>
+        <v>0.5138121630512706</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1686,6 +1846,12 @@
       <c r="K31" t="n">
         <v>1.268</v>
       </c>
+      <c r="L31" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.0416</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1702,16 +1868,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.1841254421168568</v>
+        <v>0.1841193661547154</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1539140699221879</v>
+        <v>0.1539290035337476</v>
       </c>
       <c r="F32" t="n">
-        <v>1.132693594985886</v>
+        <v>1.132322446326493</v>
       </c>
       <c r="G32" t="n">
-        <v>0.07884754352390182</v>
+        <v>0.0789404612135642</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1727,6 +1893,12 @@
       <c r="K32" t="n">
         <v>0.34</v>
       </c>
+      <c r="L32" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.1944</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1743,16 +1915,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1379464153955826</v>
+        <v>0.1379857273713067</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3157618845348849</v>
+        <v>0.3156343261295533</v>
       </c>
       <c r="F33" t="n">
-        <v>1.296695690547933</v>
+        <v>1.29770060029641</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0627731479602817</v>
+        <v>0.06259475179035502</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1768,11 +1940,17 @@
       <c r="K33" t="n">
         <v>0.219</v>
       </c>
+      <c r="L33" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.3607</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>algumas_pessoas_dizem</t>
+          <t>algumas_pessoas_dizem_2</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1784,30 +1962,36 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.3237530832134355</v>
+        <v>-0.1152176865504606</v>
       </c>
       <c r="E34" t="n">
-        <v>0.007377498521883152</v>
+        <v>0.3503875355904132</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1459217531348083</v>
+        <v>-0.34378204488842</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7893923887008276</v>
+        <v>0.559987290168392</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Qual é o seu vínculo empregatício? : +; Qual é a sua faixa etária? _46 a 55 anos: −; Você se considera uma pessoa politicamente engajada? _Sim: +</t>
+          <t>Você é homem? _Sim: −</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.289</v>
+        <v>1.265</v>
       </c>
       <c r="J34" t="n">
-        <v>1.176</v>
+        <v>1.294</v>
       </c>
       <c r="K34" t="n">
-        <v>1.099</v>
+        <v>1.368</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.7548</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.3911</v>
       </c>
     </row>
     <row r="35">
@@ -1825,16 +2009,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.2128280165889447</v>
+        <v>-0.2127077232662424</v>
       </c>
       <c r="E35" t="n">
-        <v>0.06958258807201763</v>
+        <v>0.06973247341182108</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4896614141702462</v>
+        <v>0.4888869829178522</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3998953746351624</v>
+        <v>0.4006166279447294</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1848,7 +2032,13 @@
         <v>0.588</v>
       </c>
       <c r="K35" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.093</v>
       </c>
     </row>
     <row r="36">
@@ -1866,16 +2056,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.1931403667134402</v>
+        <v>0.1932484260071904</v>
       </c>
       <c r="E36" t="n">
-        <v>0.124832075621185</v>
+        <v>0.1246355101877655</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.002704615879675111</v>
+        <v>-0.002854283925974036</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9961441781967378</v>
+        <v>0.9959308990993447</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1891,6 +2081,12 @@
       <c r="K36" t="n">
         <v>1.194</v>
       </c>
+      <c r="L36" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.1617</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1907,16 +2103,20 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.4095795771107692</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
+        <v>0.4095865909861509</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.006950322525679364</v>
+      </c>
       <c r="F37" t="n">
-        <v>-0.2867424678009972</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
+        <v>-0.2862862749644497</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.6500154640588118</v>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(nenhum)</t>
+          <t>Qual é a sua faixa etária? _Até 18 anos: −</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -1928,6 +2128,12 @@
       <c r="K37" t="n">
         <v>1.373</v>
       </c>
+      <c r="L37" t="n">
+        <v>0.8211000000000001</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.0128</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1944,16 +2150,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.5317762671307571</v>
+        <v>0.5319684217682099</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001821820860425144</v>
+        <v>0.000181464552532899</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9731796025257555</v>
+        <v>-0.9739648349547411</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1112117389761396</v>
+        <v>0.110940718086652</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1969,6 +2175,12 @@
       <c r="K38" t="n">
         <v>1.488</v>
       </c>
+      <c r="L38" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.0005</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1985,16 +2197,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.6104136691770153</v>
+        <v>0.6104738601660989</v>
       </c>
       <c r="E39" t="n">
-        <v>3.075853650597926e-05</v>
+        <v>3.071804988757359e-05</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6297770258689845</v>
+        <v>-0.6308076944179833</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3106088634258538</v>
+        <v>0.3098166061920996</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2008,7 +2220,13 @@
         <v>1.235</v>
       </c>
       <c r="K39" t="n">
-        <v>1.441</v>
+        <v>1.442</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.7082000000000001</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.0001</v>
       </c>
     </row>
     <row r="40">
@@ -2026,16 +2244,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.1692299167917824</v>
+        <v>0.1694189360148976</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4062547640123049</v>
+        <v>0.4057550535642011</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8735873975538363</v>
+        <v>0.872810133892193</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4633108441772648</v>
+        <v>0.4636107236717895</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2051,6 +2269,12 @@
       <c r="K40" t="n">
         <v>1.867</v>
       </c>
+      <c r="L40" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.4426</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2067,16 +2291,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.9454914894315256</v>
+        <v>0.9456151862507292</v>
       </c>
       <c r="E41" t="n">
-        <v>1.728970001359971e-11</v>
+        <v>1.723082562972871e-11</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9861887716446349</v>
+        <v>-0.986749496380894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.141811508258362</v>
+        <v>0.1416159364168007</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2092,6 +2316,12 @@
       <c r="K41" t="n">
         <v>1.072</v>
       </c>
+      <c r="L41" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2108,16 +2338,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.4083248098562761</v>
+        <v>0.4082783830009567</v>
       </c>
       <c r="E42" t="n">
-        <v>0.001308982098841594</v>
+        <v>0.001310243918150578</v>
       </c>
       <c r="F42" t="n">
-        <v>1.378092821140744</v>
+        <v>1.377996822955366</v>
       </c>
       <c r="G42" t="n">
-        <v>0.03671187698703091</v>
+        <v>0.0367245558323736</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2133,6 +2363,12 @@
       <c r="K42" t="n">
         <v>1.263</v>
       </c>
+      <c r="L42" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.0031</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2149,16 +2385,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.6938378944763458</v>
+        <v>0.6939223304253864</v>
       </c>
       <c r="E43" t="n">
-        <v>4.164791871890292e-07</v>
+        <v>4.157254533059676e-07</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.122950868674807</v>
+        <v>-1.123146801341886</v>
       </c>
       <c r="G43" t="n">
-        <v>0.06445752775177832</v>
+        <v>0.06441952450201389</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2174,6 +2410,12 @@
       <c r="K43" t="n">
         <v>1.252</v>
       </c>
+      <c r="L43" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2190,16 +2432,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-0.4003052328092945</v>
+        <v>-0.4003512820135568</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00156536850041348</v>
+        <v>0.001563611855224262</v>
       </c>
       <c r="F44" t="n">
-        <v>1.07455456978932</v>
+        <v>1.074687691036678</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1097142103970869</v>
+        <v>0.109672316550967</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2215,6 +2457,12 @@
       <c r="K44" t="n">
         <v>1.486</v>
       </c>
+      <c r="L44" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.0036</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2231,16 +2479,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-1.258270893794168</v>
+        <v>-1.25778632181573</v>
       </c>
       <c r="E45" t="n">
-        <v>4.620971507380195e-10</v>
+        <v>4.639780698817341e-10</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9794910783646782</v>
+        <v>0.9786200891446978</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1535143496120978</v>
+        <v>0.1537791186280926</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2256,6 +2504,12 @@
       <c r="K45" t="n">
         <v>0.661</v>
       </c>
+      <c r="L45" t="n">
+        <v>0.5272</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2272,16 +2526,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-0.610287696976735</v>
+        <v>-0.6104812885751822</v>
       </c>
       <c r="E46" t="n">
-        <v>2.341568124344258e-06</v>
+        <v>2.329651806044052e-06</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.07640322944307949</v>
+        <v>-0.07568641405192603</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8973706233255634</v>
+        <v>0.898337243253434</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2297,6 +2551,12 @@
       <c r="K46" t="n">
         <v>0.71</v>
       </c>
+      <c r="L46" t="n">
+        <v>0.9785</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2313,16 +2573,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.123297808708285</v>
+        <v>-0.1232979778677589</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2982482354107212</v>
+        <v>0.2982495928042298</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6728813488550853</v>
+        <v>0.6729911757878515</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2617309419040669</v>
+        <v>0.2616558419691121</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2338,6 +2598,12 @@
       <c r="K47" t="n">
         <v>1.343</v>
       </c>
+      <c r="L47" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.3492</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2354,16 +2620,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.6280235745254971</v>
+        <v>-0.6280417117032373</v>
       </c>
       <c r="E48" t="n">
-        <v>3.673842961900069e-07</v>
+        <v>3.674687503954325e-07</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6615112050284808</v>
+        <v>-0.6617366552147508</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2526773783350194</v>
+        <v>0.252522724868078</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2379,6 +2645,12 @@
       <c r="K48" t="n">
         <v>1.22</v>
       </c>
+      <c r="L48" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2395,16 +2667,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.3396156184497587</v>
+        <v>-0.3396298671912385</v>
       </c>
       <c r="E49" t="n">
-        <v>0.004416976830140781</v>
+        <v>0.004415043840201916</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.3964016354650249</v>
+        <v>-0.3970388823567919</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4720327328203165</v>
+        <v>0.4713131630042769</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2420,6 +2692,12 @@
       <c r="K49" t="n">
         <v>1.315</v>
       </c>
+      <c r="L49" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.008800000000000001</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2436,16 +2714,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-0.8071615026699207</v>
+        <v>-0.8070765674628881</v>
       </c>
       <c r="E50" t="n">
-        <v>1.884472413247017e-09</v>
+        <v>1.889998523285483e-09</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5267422415258384</v>
+        <v>0.5265877394284432</v>
       </c>
       <c r="G50" t="n">
-        <v>0.401317556299721</v>
+        <v>0.4014501723526321</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2461,6 +2739,12 @@
       <c r="K50" t="n">
         <v>0.973</v>
       </c>
+      <c r="L50" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2477,13 +2761,17 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.619275318999681</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
+        <v>0.6192693995935663</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.001816815042822222</v>
+      </c>
       <c r="F51" t="n">
-        <v>0.7578026603455209</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
+        <v>0.7586282822200512</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.417654828977458</v>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>(nenhum)</t>
@@ -2498,6 +2786,12 @@
       <c r="K51" t="n">
         <v>1.78</v>
       </c>
+      <c r="L51" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.004</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2514,16 +2808,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-0.6151615344761512</v>
+        <v>-0.6150223863226288</v>
       </c>
       <c r="E52" t="n">
-        <v>4.218609710682496e-06</v>
+        <v>4.233028707404759e-06</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.489817331696545</v>
+        <v>-0.4893962628786622</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4250347914510672</v>
+        <v>0.4254042808319235</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2539,6 +2833,12 @@
       <c r="K52" t="n">
         <v>0.837</v>
       </c>
+      <c r="L52" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2555,16 +2855,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-0.3367303323600209</v>
+        <v>-0.3367619139936798</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02507845720133885</v>
+        <v>0.02506708442500117</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.6153029483565332</v>
+        <v>-0.6136974562492458</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4379692328917992</v>
+        <v>0.4390712895696757</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2580,6 +2880,12 @@
       <c r="K53" t="n">
         <v>0.342</v>
       </c>
+      <c r="L53" t="n">
+        <v>0.7522</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.0401</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2596,16 +2902,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.6461525377263307</v>
+        <v>0.6462537795630576</v>
       </c>
       <c r="E54" t="n">
-        <v>3.973673281501834e-06</v>
+        <v>3.961800800799931e-06</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2236088490770424</v>
+        <v>0.2242362603292211</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7133896802749051</v>
+        <v>0.7126316136884299</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2620,6 +2926,12 @@
       </c>
       <c r="K54" t="n">
         <v>1.393</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.8552</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
